--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129751764</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751774</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129751771</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>129751772</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129751761</v>
       </c>
       <c r="B9" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129751768</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129751765</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>129751769</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>129751770</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>88986</v>
+        <v>88987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751763</v>
+        <v>129751773</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462321</v>
+        <v>462435</v>
       </c>
       <c r="R16" t="n">
-        <v>7058853</v>
+        <v>7059322</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751773</v>
+        <v>129751763</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462435</v>
+        <v>462321</v>
       </c>
       <c r="R17" t="n">
-        <v>7059322</v>
+        <v>7058853</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2271,6 +2271,124 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129773243</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nytjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>462329</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7058906</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sittande högt upp i en gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129751774</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129751771</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>129751772</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129751761</v>
       </c>
       <c r="B9" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129751768</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>129751769</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>129751770</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91959</v>
+        <v>91964</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>88987</v>
+        <v>88992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129751773</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R4" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,23 +987,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R5" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -914,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R4" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,19 +983,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R5" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751772</v>
+        <v>129751761</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462349</v>
+        <v>462240</v>
       </c>
       <c r="R8" t="n">
-        <v>7059243</v>
+        <v>7059162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1370,10 +1365,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751761</v>
+        <v>129751772</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1376,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462240</v>
+        <v>462349</v>
       </c>
       <c r="R9" t="n">
-        <v>7059162</v>
+        <v>7059243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,6 +1436,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R4" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,23 +987,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R5" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751761</v>
+        <v>129751772</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462240</v>
+        <v>462349</v>
       </c>
       <c r="R8" t="n">
-        <v>7059162</v>
+        <v>7059243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1339,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1365,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751772</v>
+        <v>129751761</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1376,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1400,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462349</v>
+        <v>462240</v>
       </c>
       <c r="R9" t="n">
-        <v>7059243</v>
+        <v>7059162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,11 +1441,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2070,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751773</v>
+        <v>129751763</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462435</v>
+        <v>462321</v>
       </c>
       <c r="R16" t="n">
-        <v>7059322</v>
+        <v>7058853</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751763</v>
+        <v>129751773</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462321</v>
+        <v>462435</v>
       </c>
       <c r="R17" t="n">
-        <v>7058853</v>
+        <v>7059322</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129751760</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129751766</v>
       </c>
       <c r="B5" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129751761</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91964</v>
+        <v>91968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129751760</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129751766</v>
       </c>
       <c r="B5" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751772</v>
+        <v>129751761</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462349</v>
+        <v>462240</v>
       </c>
       <c r="R8" t="n">
-        <v>7059243</v>
+        <v>7059162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1370,10 +1365,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751761</v>
+        <v>129751772</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1376,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462240</v>
+        <v>462349</v>
       </c>
       <c r="R9" t="n">
-        <v>7059162</v>
+        <v>7059243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,6 +1436,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91968</v>
+        <v>91970</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751763</v>
+        <v>129751773</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462321</v>
+        <v>462435</v>
       </c>
       <c r="R16" t="n">
-        <v>7058853</v>
+        <v>7059322</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751773</v>
+        <v>129751763</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462435</v>
+        <v>462321</v>
       </c>
       <c r="R17" t="n">
-        <v>7059322</v>
+        <v>7058853</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>91619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -914,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R4" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91619</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,19 +983,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R5" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751761</v>
+        <v>129751772</v>
       </c>
       <c r="B8" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462240</v>
+        <v>462349</v>
       </c>
       <c r="R8" t="n">
-        <v>7059162</v>
+        <v>7059243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1339,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1365,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751772</v>
+        <v>129751761</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1376,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1400,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462349</v>
+        <v>462240</v>
       </c>
       <c r="R9" t="n">
-        <v>7059243</v>
+        <v>7059162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,11 +1441,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2070,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751773</v>
+        <v>129751763</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462435</v>
+        <v>462321</v>
       </c>
       <c r="R16" t="n">
-        <v>7059322</v>
+        <v>7058853</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751763</v>
+        <v>129751773</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462321</v>
+        <v>462435</v>
       </c>
       <c r="R17" t="n">
-        <v>7058853</v>
+        <v>7059322</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751764</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751774</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129751771</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751772</v>
+        <v>129751761</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462349</v>
+        <v>462240</v>
       </c>
       <c r="R8" t="n">
-        <v>7059243</v>
+        <v>7059162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1370,10 +1365,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751761</v>
+        <v>129751772</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1376,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462240</v>
+        <v>462349</v>
       </c>
       <c r="R9" t="n">
-        <v>7059162</v>
+        <v>7059243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,6 +1436,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,7 +1470,7 @@
         <v>129751768</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129751765</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>129751769</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>129751770</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>88998</v>
+        <v>89001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751763</v>
+        <v>129751773</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462321</v>
+        <v>462435</v>
       </c>
       <c r="R16" t="n">
-        <v>7058853</v>
+        <v>7059322</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751773</v>
+        <v>129751763</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462435</v>
+        <v>462321</v>
       </c>
       <c r="R17" t="n">
-        <v>7059322</v>
+        <v>7058853</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,7 +2277,7 @@
         <v>129773243</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -2070,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751773</v>
+        <v>129751763</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462435</v>
+        <v>462321</v>
       </c>
       <c r="R16" t="n">
-        <v>7059322</v>
+        <v>7058853</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751763</v>
+        <v>129751773</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462321</v>
+        <v>462435</v>
       </c>
       <c r="R17" t="n">
-        <v>7058853</v>
+        <v>7059322</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129751764</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129751774</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B4" t="n">
-        <v>91622</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R4" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,23 +987,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R5" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129751771</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>129751761</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129751772</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129751768</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>129751765</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>129751769</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>129751770</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91973</v>
+        <v>91976</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>89001</v>
+        <v>89004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129751763</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>129751773</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>129773243</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -914,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R4" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91625</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,19 +983,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R5" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129751774</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129751771</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751761</v>
+        <v>129751772</v>
       </c>
       <c r="B8" t="n">
-        <v>91605</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462240</v>
+        <v>462349</v>
       </c>
       <c r="R8" t="n">
-        <v>7059162</v>
+        <v>7059243</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,6 +1339,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1365,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751772</v>
+        <v>129751761</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>91606</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1376,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1400,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462349</v>
+        <v>462240</v>
       </c>
       <c r="R9" t="n">
-        <v>7059243</v>
+        <v>7059162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,11 +1441,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1470,7 +1470,7 @@
         <v>129751768</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>129751769</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>129751770</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91976</v>
+        <v>91977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>89004</v>
+        <v>89005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751763</v>
+        <v>129751773</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>462321</v>
+        <v>462435</v>
       </c>
       <c r="R16" t="n">
-        <v>7058853</v>
+        <v>7059322</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751773</v>
+        <v>129751763</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,21 +2183,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462435</v>
+        <v>462321</v>
       </c>
       <c r="R17" t="n">
-        <v>7059322</v>
+        <v>7058853</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -1268,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751772</v>
+        <v>129751761</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>91606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462349</v>
+        <v>462240</v>
       </c>
       <c r="R8" t="n">
-        <v>7059243</v>
+        <v>7059162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1339,11 +1339,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1370,10 +1365,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751761</v>
+        <v>129751772</v>
       </c>
       <c r="B9" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1376,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462240</v>
+        <v>462349</v>
       </c>
       <c r="R9" t="n">
-        <v>7059162</v>
+        <v>7059243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1441,6 +1436,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B4" t="n">
-        <v>91626</v>
+        <v>91606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,19 +890,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -910,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R4" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>91626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -983,23 +987,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R5" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 36272-2024 artfynd.xlsx
+++ b/artfynd/A 36272-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129751774</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751760</v>
+        <v>129751766</v>
       </c>
       <c r="B4" t="n">
-        <v>91606</v>
+        <v>91643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,23 +890,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -914,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462324</v>
+        <v>462243</v>
       </c>
       <c r="R4" t="n">
-        <v>7058871</v>
+        <v>7058850</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129751766</v>
+        <v>129751760</v>
       </c>
       <c r="B5" t="n">
-        <v>91626</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,19 +983,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462243</v>
+        <v>462324</v>
       </c>
       <c r="R5" t="n">
-        <v>7058850</v>
+        <v>7058871</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1072,7 @@
         <v>129751762</v>
       </c>
       <c r="B6" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>129751771</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>129751761</v>
       </c>
       <c r="B8" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129751772</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129751768</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>129751769</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>129751770</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129751759</v>
       </c>
       <c r="B14" t="n">
-        <v>91977</v>
+        <v>91994</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>129751775</v>
       </c>
       <c r="B15" t="n">
-        <v>89005</v>
+        <v>89022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>129751773</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
